--- a/CSV Reader/TestFile.xlsx
+++ b/CSV Reader/TestFile.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Devpriya\Documents\Code\Github Local\PRISM-AI\CSV Reader\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26FFCA95-39C2-42D3-80C2-33C9030E9015}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D75DD07-BEA6-469F-996D-83CD964BFC2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{50E4AFCB-EC5A-4C8D-A63C-8F7FCEAA6D44}"/>
   </bookViews>
@@ -52,7 +52,7 @@
     <t>devkulemannege@gmail.com</t>
   </si>
   <si>
-    <t>First Name</t>
+    <t xml:space="preserve">First Name </t>
   </si>
 </sst>
 </file>
